--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,40 +478,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arrindell</t>
+          <t>f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>744943369</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dfsq</t>
+          <t>q</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SDA</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>erick_eapa@outlook.com</t>
+          <t>tqu59190@gmail.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UmoIhIo47v</t>
+          <t>tpS1V7GKii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>supprimé_def</t>
+          <t>supprimé</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -523,35 +523,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>POLANCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>744943369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>Accumed</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>tqu59190@gmail.com</t>
+          <t>erick_eapa@outlook.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tpS1V7GKii</t>
+          <t>098765</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -561,7 +561,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>flooerlemans16@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>744943369</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dfgfs</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>erick.gargolas@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xrciyZ8hEl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>supprimé_def</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
         </is>
       </c>
     </row>

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>supprimé</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POLANCO</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,48 +536,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Accumed</t>
+          <t>dfgfs</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>erick_eapa@outlook.com</t>
+          <t>erick.gargolas@gmail.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>098765</t>
+          <t>xrciyZ8hEl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>supprimé_def</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>OERLEMANS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Flo</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>695552123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>c3S4DCYZVo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -613,12 +613,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Arrindell</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -626,32 +626,167 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dfgfs</t>
+          <t>sdfsdf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>erick.gargolas@gmail.com</t>
+          <t>asdas@sdsdf.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xrciyZ8hEl</t>
+          <t>y4wouKe0tE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arrindell</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>744943369</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fsefsd</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>fsd</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>dgd@dfdfg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>koDIMwUYbI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>supprimé_def</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>695552123</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>flooerlemans@outlook.fr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>jUwN9spXOC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Arrindell</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>744943369</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dfgfdg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dsfsd</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>jose@accumed.com</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>65fPU4jRDv</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
         </is>
       </c>
     </row>

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>supprimé</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,35 +568,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OERLEMANS</t>
+          <t>Arrindell</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Flo</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>695552123</v>
+        <v>744943369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>sdfsdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>flooerlemans16@gmail.com</t>
+          <t>asdas@sdsdf.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c3S4DCYZVo</t>
+          <t>y4wouKe0tE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -626,67 +626,67 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sdfsdf</t>
+          <t>fsefsd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>fsd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>asdas@sdsdf.com</t>
+          <t>dgd@dfdfg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>y4wouKe0tE</t>
+          <t>koDIMwUYbI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>supprimé_def</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arrindell</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>744943369</v>
+        <v>695552123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>fsefsd</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fsd</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>dgd@dfdfg</t>
+          <t>flooerlemans@outlook.fr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>koDIMwUYbI</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -703,35 +703,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Arrindell</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>695552123</v>
+        <v>744943369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>dfgfdg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>dsfsd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>flooerlemans@outlook.fr</t>
+          <t>jose@accumed.com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jUwN9spXOC</t>
+          <t>65fPU4jRDv</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -748,43 +748,88 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arrindell</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>744943369</v>
+        <v>695552123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dfgfdg</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dsfsd</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>jose@accumed.com</t>
+          <t>flooerlemans16@gmail.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>65fPU4jRDv</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>supprimé</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OERLEMANS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Flo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>695552123</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>flooerlemans01@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ORjNWvNaqr</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,15 +461,10 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Statut</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Date Création</t>
         </is>
@@ -506,15 +501,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>tpS1V7GKii</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>2025-06-14</t>
         </is>
@@ -551,15 +541,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>xrciyZ8hEl</t>
+          <t>supprimé_def</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>supprimé_def</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>2025-06-16</t>
         </is>
@@ -596,15 +581,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>y4wouKe0tE</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>2025-06-16</t>
         </is>
@@ -641,15 +621,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>koDIMwUYbI</t>
+          <t>supprimé_def</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>supprimé_def</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>
@@ -686,15 +661,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>supprimé_def</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>supprimé_def</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>
@@ -731,15 +701,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>65fPU4jRDv</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>
@@ -776,15 +741,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>
@@ -821,17 +781,52 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ORjNWvNaqr</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arrindell</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>744943369</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dfgd</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sdfsd</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>erick@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
         </is>
       </c>
     </row>

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>supprimé</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>désactivé</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>Date Création</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>désactivé</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -509,6 +514,7 @@
           <t>2025-06-14</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +555,7 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,6 +596,7 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -629,6 +637,7 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -669,6 +678,7 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -709,6 +719,7 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -749,6 +760,7 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -789,6 +801,7 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -829,6 +842,175 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>asda</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>asda</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1234567890</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>asda</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vcd</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>650908504</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>cd</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>evaqu185@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>csc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>scs</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>650908504</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dzd</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1234@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3QjIl6gWU8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dsf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ff</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>650908504</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>fzef</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dfd</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>12345@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,7 +924,11 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1011,6 +1015,88 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fdz</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fz</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>650908504</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fs</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>dfs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>xiangtong.qu@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ef</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fz</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>650908504</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rz</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>quxiangtong@163.com</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>supprimé_def</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -847,30 +847,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>asda</t>
+          <t>vcd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>asda</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1234567890</v>
+        <v>650908504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>asda</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sada</t>
+          <t>cd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>erick_eapa@outlook.com</t>
+          <t>evaqu185@gmail.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -883,17 +883,21 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vcd</t>
+          <t>csc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>scs</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -901,17 +905,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>dzd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>cs</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>cd</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>evaqu185@gmail.com</t>
+          <t>1234@gmail.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -926,19 +930,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>3QjIl6gWU8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>csc</t>
+          <t>dsf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>scs</t>
+          <t>ff</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -946,17 +950,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>dzd</t>
+          <t>fzef</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>cs</t>
+          <t>dfd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1234@gmail.com</t>
+          <t>12345@gmail.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -969,21 +973,17 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3QjIl6gWU8</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dsf</t>
+          <t>fdz</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ff</t>
+          <t>fz</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -991,17 +991,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>fzef</t>
+          <t>fs</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>dfd</t>
+          <t>dfs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>12345@gmail.com</t>
+          <t>xiangtong.qu@epfedu.fr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fdz</t>
+          <t>ef</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>dz</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>dfs</t>
+          <t>rz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>xiangtong.qu@epfedu.fr</t>
+          <t>quxiangtong@163.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1060,30 +1060,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ef</t>
+          <t>Arrindell</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fz</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>650908504</v>
+        <v>744943369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dz</t>
+          <t>asdas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rz</t>
+          <t>sdasd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>quxiangtong@163.com</t>
+          <t>erick_eapa@outlook.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1096,7 +1096,11 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/accepted_user_information.xlsx
+++ b/static/accepted_user_information.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,101 +461,109 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Hashed Password</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Date Création</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Password</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Arrindell</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>744943369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>sfsd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>adas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>tqu59190@gmail.com</t>
+          <t>erick_eapa@outlook.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>désactivé</t>
+          <t>$2b$12$J.yyOTNIYKVYBE4Wuj3MHOpGmNFPNdlZtH0kBVOqWDudqu.uFQpVq</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>OER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Flo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>744943369</v>
+        <v>695552123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dfgfs</t>
+          <t>Epf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>erick.gargolas@gmail.com</t>
+          <t>flooerlemans16@gmail.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>supprimé_def</t>
+          <t>$2b$12$jsmmZvNo/WFmDih3v07DbOq3uyfWZxBBUKL1i2KdbnSkEc0EJFetC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,532 +581,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sdfsdf</t>
+          <t>example</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>example</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>asdas@sdsdf.com</t>
+          <t>eduardoantonio.polancoarrindell@epfedu.fr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>supprimé</t>
+          <t>$2b$12$Q1zXu6OAZRGUE8xXMvND.epPqZgPGwCYqIAwqt5FShUURasXisd/2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Arrindell</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eduardo</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>744943369</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>fsefsd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>fsd</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>dgd@dfdfg</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>supprimé_def</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>695552123</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>flooerlemans@outlook.fr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>supprimé_def</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Arrindell</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Eduardo</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>744943369</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>dfgfdg</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>dsfsd</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>jose@accumed.com</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>actif</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>695552123</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>flooerlemans16@gmail.com</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>OERLEMANS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Flo</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>695552123</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>flooerlemans01@gmail.com</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>supprimé_def</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Arrindell</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Eduardo</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>744943369</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>dfgd</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sdfsd</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>erick@gmail.com</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>désactivé</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>vcd</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>650908504</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>cd</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>evaqu185@gmail.com</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>csc</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>scs</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>650908504</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>dzd</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>cs</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1234@gmail.com</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3QjIl6gWU8</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dsf</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ff</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>650908504</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>fzef</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>dfd</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>12345@gmail.com</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>fdz</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>fz</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>650908504</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>fs</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>dfs</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>xiangtong.qu@epfedu.fr</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ef</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fz</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>650908504</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>rz</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>quxiangtong@163.com</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Arrindell</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Eduardo</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>744943369</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>asdas</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>sdasd</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>erick_eapa@outlook.com</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>actif</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>123456</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
         </is>
       </c>
     </row>
